--- a/tutor/初中数学/中考试卷各知识点占比.xlsx
+++ b/tutor/初中数学/中考试卷各知识点占比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="展示表" sheetId="1" r:id="rId1"/>
@@ -1252,9 +1252,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B7:P37"/>
+  <dimension ref="B7:P38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="10.25" customWidth="1"/>
@@ -1268,6 +1269,7 @@
     <col min="14" max="14" width="10.875" customWidth="1"/>
     <col min="15" max="15" width="10.75" customWidth="1"/>
     <col min="16" max="16" width="12.875" customWidth="1"/>
+    <col min="17" max="17" width="4.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
@@ -1340,7 +1342,7 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="2:16">
       <c r="B9" s="6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9" s="24" t="str">
         <f>原表!C6&amp;IF(原表!C6/150=0,"","/"&amp;TEXT(原表!C6/150,IF(MOD(原表!C6/150,0.01)=0,"0%","0.00%")))</f>
@@ -1348,7 +1350,7 @@
       </c>
       <c r="D9" s="24" t="str">
         <f>原表!D6&amp;IF(原表!D6/150=0,"","/"&amp;TEXT(原表!D6/150,IF(MOD(原表!D6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>16/10.67%</v>
+        <v>20/13.33%</v>
       </c>
       <c r="E9" s="24" t="str">
         <f>原表!E6&amp;IF(原表!E6/150=0,"","/"&amp;TEXT(原表!E6/150,IF(MOD(原表!E6/150,0.01)=0,"0%","0.00%")))</f>
@@ -1360,7 +1362,7 @@
       </c>
       <c r="G9" s="24" t="str">
         <f>原表!G6&amp;IF(原表!G6/150=0,"","/"&amp;TEXT(原表!G6/150,IF(MOD(原表!G6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>0</v>
       </c>
       <c r="H9" s="24" t="str">
         <f>原表!H6&amp;IF(原表!H6/150=0,"","/"&amp;TEXT(原表!H6/150,IF(MOD(原表!H6/150,0.01)=0,"0%","0.00%")))</f>
@@ -1372,7 +1374,7 @@
       </c>
       <c r="J9" s="24" t="str">
         <f>原表!J6&amp;IF(原表!J6/150=0,"","/"&amp;TEXT(原表!J6/150,IF(MOD(原表!J6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>19/12.67%</v>
       </c>
       <c r="K9" s="24" t="str">
         <f>原表!K6&amp;IF(原表!K6/150=0,"","/"&amp;TEXT(原表!K6/150,IF(MOD(原表!K6/150,0.01)=0,"0%","0.00%")))</f>
@@ -1380,11 +1382,11 @@
       </c>
       <c r="L9" s="24" t="str">
         <f>原表!L6&amp;IF(原表!L6/150=0,"","/"&amp;TEXT(原表!L6/150,IF(MOD(原表!L6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>8/5.33%</v>
+        <v>0</v>
       </c>
       <c r="M9" s="24" t="str">
         <f>原表!M6&amp;IF(原表!M6/150=0,"","/"&amp;TEXT(原表!M6/150,IF(MOD(原表!M6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>14/9.33%</v>
       </c>
       <c r="N9" s="24" t="str">
         <f>原表!N6&amp;IF(原表!N6/150=0,"","/"&amp;TEXT(原表!N6/150,IF(MOD(原表!N6/150,0.01)=0,"0%","0.00%")))</f>
@@ -1396,36 +1398,36 @@
       </c>
       <c r="P9" s="24" t="str">
         <f>原表!P6&amp;IF(原表!P6/150=0,"","/"&amp;TEXT(原表!P6/150,IF(MOD(原表!P6/150,0.01)=0,"0%","0.00%")))</f>
-        <v>32/21.33%</v>
+        <v>28/18.67%</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="2:16">
       <c r="B10" s="6">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C10" s="24" t="str">
         <f>原表!C7&amp;IF(原表!C7/150=0,"","/"&amp;TEXT(原表!C7/150,IF(MOD(原表!C7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>42/28%</v>
+        <v>46/30.67%</v>
       </c>
       <c r="D10" s="24" t="str">
         <f>原表!D7&amp;IF(原表!D7/150=0,"","/"&amp;TEXT(原表!D7/150,IF(MOD(原表!D7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>16/10.67%</v>
       </c>
       <c r="E10" s="24" t="str">
         <f>原表!E7&amp;IF(原表!E7/150=0,"","/"&amp;TEXT(原表!E7/150,IF(MOD(原表!E7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>0</v>
       </c>
       <c r="F10" s="24" t="str">
         <f>原表!F7&amp;IF(原表!F7/150=0,"","/"&amp;TEXT(原表!F7/150,IF(MOD(原表!F7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>4/2.67%</v>
       </c>
       <c r="G10" s="24" t="str">
         <f>原表!G7&amp;IF(原表!G7/150=0,"","/"&amp;TEXT(原表!G7/150,IF(MOD(原表!G7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>4/2.67%</v>
       </c>
       <c r="H10" s="24" t="str">
         <f>原表!H7&amp;IF(原表!H7/150=0,"","/"&amp;TEXT(原表!H7/150,IF(MOD(原表!H7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>28/18.67%</v>
+        <v>24/16%</v>
       </c>
       <c r="I10" s="24" t="str">
         <f>原表!I7&amp;IF(原表!I7/150=0,"","/"&amp;TEXT(原表!I7/150,IF(MOD(原表!I7/150,0.01)=0,"0%","0.00%")))</f>
@@ -1441,11 +1443,11 @@
       </c>
       <c r="L10" s="24" t="str">
         <f>原表!L7&amp;IF(原表!L7/150=0,"","/"&amp;TEXT(原表!L7/150,IF(MOD(原表!L7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>8/5.33%</v>
       </c>
       <c r="M10" s="24" t="str">
         <f>原表!M7&amp;IF(原表!M7/150=0,"","/"&amp;TEXT(原表!M7/150,IF(MOD(原表!M7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>16/10.67%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="N10" s="24" t="str">
         <f>原表!N7&amp;IF(原表!N7/150=0,"","/"&amp;TEXT(原表!N7/150,IF(MOD(原表!N7/150,0.01)=0,"0%","0.00%")))</f>
@@ -1457,24 +1459,24 @@
       </c>
       <c r="P10" s="24" t="str">
         <f>原表!P7&amp;IF(原表!P7/150=0,"","/"&amp;TEXT(原表!P7/150,IF(MOD(原表!P7/150,0.01)=0,"0%","0.00%")))</f>
-        <v>34/22.67%</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="18" spans="2:16">
+        <v>32/21.33%</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="2:16">
       <c r="B11" s="6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11" s="24" t="str">
         <f>原表!C8&amp;IF(原表!C8/150=0,"","/"&amp;TEXT(原表!C8/150,IF(MOD(原表!C8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>43/28.67%</v>
+        <v>42/28%</v>
       </c>
       <c r="D11" s="24" t="str">
         <f>原表!D8&amp;IF(原表!D8/150=0,"","/"&amp;TEXT(原表!D8/150,IF(MOD(原表!D8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>18/12%</v>
       </c>
       <c r="E11" s="24" t="str">
         <f>原表!E8&amp;IF(原表!E8/150=0,"","/"&amp;TEXT(原表!E8/150,IF(MOD(原表!E8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>4/2.67%</v>
       </c>
       <c r="F11" s="24" t="str">
         <f>原表!F8&amp;IF(原表!F8/150=0,"","/"&amp;TEXT(原表!F8/150,IF(MOD(原表!F8/150,0.01)=0,"0%","0.00%")))</f>
@@ -1482,15 +1484,15 @@
       </c>
       <c r="G11" s="24" t="str">
         <f>原表!G8&amp;IF(原表!G8/150=0,"","/"&amp;TEXT(原表!G8/150,IF(MOD(原表!G8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>0</v>
       </c>
       <c r="H11" s="24" t="str">
         <f>原表!H8&amp;IF(原表!H8/150=0,"","/"&amp;TEXT(原表!H8/150,IF(MOD(原表!H8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>19/12.67%</v>
+        <v>28/18.67%</v>
       </c>
       <c r="I11" s="24" t="str">
         <f>原表!I8&amp;IF(原表!I8/150=0,"","/"&amp;TEXT(原表!I8/150,IF(MOD(原表!I8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>13/8.67%</v>
+        <v>9/6%</v>
       </c>
       <c r="J11" s="24" t="str">
         <f>原表!J8&amp;IF(原表!J8/150=0,"","/"&amp;TEXT(原表!J8/150,IF(MOD(原表!J8/150,0.01)=0,"0%","0.00%")))</f>
@@ -1498,15 +1500,15 @@
       </c>
       <c r="K11" s="24" t="str">
         <f>原表!K8&amp;IF(原表!K8/150=0,"","/"&amp;TEXT(原表!K8/150,IF(MOD(原表!K8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>51/34%</v>
+        <v>56/37.33%</v>
       </c>
       <c r="L11" s="24" t="str">
         <f>原表!L8&amp;IF(原表!L8/150=0,"","/"&amp;TEXT(原表!L8/150,IF(MOD(原表!L8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="M11" s="24" t="str">
         <f>原表!M8&amp;IF(原表!M8/150=0,"","/"&amp;TEXT(原表!M8/150,IF(MOD(原表!M8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>9/6%</v>
+        <v>16/10.67%</v>
       </c>
       <c r="N11" s="24" t="str">
         <f>原表!N8&amp;IF(原表!N8/150=0,"","/"&amp;TEXT(原表!N8/150,IF(MOD(原表!N8/150,0.01)=0,"0%","0.00%")))</f>
@@ -1518,16 +1520,16 @@
       </c>
       <c r="P11" s="24" t="str">
         <f>原表!P8&amp;IF(原表!P8/150=0,"","/"&amp;TEXT(原表!P8/150,IF(MOD(原表!P8/150,0.01)=0,"0%","0.00%")))</f>
-        <v>41/27.33%</v>
+        <v>34/22.67%</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="18" spans="2:16">
       <c r="B12" s="6">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C12" s="24" t="str">
         <f>原表!C9&amp;IF(原表!C9/150=0,"","/"&amp;TEXT(原表!C9/150,IF(MOD(原表!C9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>44/29.33%</v>
+        <v>43/28.67%</v>
       </c>
       <c r="D12" s="24" t="str">
         <f>原表!D9&amp;IF(原表!D9/150=0,"","/"&amp;TEXT(原表!D9/150,IF(MOD(原表!D9/150,0.01)=0,"0%","0.00%")))</f>
@@ -1535,23 +1537,23 @@
       </c>
       <c r="E12" s="24" t="str">
         <f>原表!E9&amp;IF(原表!E9/150=0,"","/"&amp;TEXT(原表!E9/150,IF(MOD(原表!E9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>0</v>
       </c>
       <c r="F12" s="24" t="str">
         <f>原表!F9&amp;IF(原表!F9/150=0,"","/"&amp;TEXT(原表!F9/150,IF(MOD(原表!F9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>0</v>
       </c>
       <c r="G12" s="24" t="str">
         <f>原表!G9&amp;IF(原表!G9/150=0,"","/"&amp;TEXT(原表!G9/150,IF(MOD(原表!G9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="H12" s="24" t="str">
         <f>原表!H9&amp;IF(原表!H9/150=0,"","/"&amp;TEXT(原表!H9/150,IF(MOD(原表!H9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>16/10.67%</v>
+        <v>19/12.67%</v>
       </c>
       <c r="I12" s="24" t="str">
         <f>原表!I9&amp;IF(原表!I9/150=0,"","/"&amp;TEXT(原表!I9/150,IF(MOD(原表!I9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>13/8.67%</v>
       </c>
       <c r="J12" s="24" t="str">
         <f>原表!J9&amp;IF(原表!J9/150=0,"","/"&amp;TEXT(原表!J9/150,IF(MOD(原表!J9/150,0.01)=0,"0%","0.00%")))</f>
@@ -1559,19 +1561,19 @@
       </c>
       <c r="K12" s="24" t="str">
         <f>原表!K9&amp;IF(原表!K9/150=0,"","/"&amp;TEXT(原表!K9/150,IF(MOD(原表!K9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>56/37.33%</v>
+        <v>51/34%</v>
       </c>
       <c r="L12" s="24" t="str">
         <f>原表!L9&amp;IF(原表!L9/150=0,"","/"&amp;TEXT(原表!L9/150,IF(MOD(原表!L9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>18/12%</v>
       </c>
       <c r="M12" s="24" t="str">
         <f>原表!M9&amp;IF(原表!M9/150=0,"","/"&amp;TEXT(原表!M9/150,IF(MOD(原表!M9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>9/6%</v>
       </c>
       <c r="N12" s="24" t="str">
         <f>原表!N9&amp;IF(原表!N9/150=0,"","/"&amp;TEXT(原表!N9/150,IF(MOD(原表!N9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="O12" s="24" t="str">
         <f>原表!O9&amp;IF(原表!O9/150=0,"","/"&amp;TEXT(原表!O9/150,IF(MOD(原表!O9/150,0.01)=0,"0%","0.00%")))</f>
@@ -1579,16 +1581,16 @@
       </c>
       <c r="P12" s="24" t="str">
         <f>原表!P9&amp;IF(原表!P9/150=0,"","/"&amp;TEXT(原表!P9/150,IF(MOD(原表!P9/150,0.01)=0,"0%","0.00%")))</f>
-        <v>35/23.33%</v>
+        <v>41/27.33%</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="18" spans="2:16">
       <c r="B13" s="6">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C13" s="24" t="str">
         <f>原表!C10&amp;IF(原表!C10/150=0,"","/"&amp;TEXT(原表!C10/150,IF(MOD(原表!C10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>43/28.67%</v>
+        <v>44/29.33%</v>
       </c>
       <c r="D13" s="24" t="str">
         <f>原表!D10&amp;IF(原表!D10/150=0,"","/"&amp;TEXT(原表!D10/150,IF(MOD(原表!D10/150,0.01)=0,"0%","0.00%")))</f>
@@ -1596,7 +1598,7 @@
       </c>
       <c r="E13" s="24" t="str">
         <f>原表!E10&amp;IF(原表!E10/150=0,"","/"&amp;TEXT(原表!E10/150,IF(MOD(原表!E10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>5/3.33%</v>
       </c>
       <c r="F13" s="24" t="str">
         <f>原表!F10&amp;IF(原表!F10/150=0,"","/"&amp;TEXT(原表!F10/150,IF(MOD(原表!F10/150,0.01)=0,"0%","0.00%")))</f>
@@ -1608,31 +1610,31 @@
       </c>
       <c r="H13" s="24" t="str">
         <f>原表!H10&amp;IF(原表!H10/150=0,"","/"&amp;TEXT(原表!H10/150,IF(MOD(原表!H10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>16/10.67%</v>
       </c>
       <c r="I13" s="24" t="str">
         <f>原表!I10&amp;IF(原表!I10/150=0,"","/"&amp;TEXT(原表!I10/150,IF(MOD(原表!I10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="J13" s="24" t="str">
         <f>原表!J10&amp;IF(原表!J10/150=0,"","/"&amp;TEXT(原表!J10/150,IF(MOD(原表!J10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>11/7.33%</v>
+        <v>15/10%</v>
       </c>
       <c r="K13" s="24" t="str">
         <f>原表!K10&amp;IF(原表!K10/150=0,"","/"&amp;TEXT(原表!K10/150,IF(MOD(原表!K10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>51/34%</v>
+        <v>56/37.33%</v>
       </c>
       <c r="L13" s="24" t="str">
         <f>原表!L10&amp;IF(原表!L10/150=0,"","/"&amp;TEXT(原表!L10/150,IF(MOD(原表!L10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="M13" s="24" t="str">
         <f>原表!M10&amp;IF(原表!M10/150=0,"","/"&amp;TEXT(原表!M10/150,IF(MOD(原表!M10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>12/8%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="N13" s="24" t="str">
         <f>原表!N10&amp;IF(原表!N10/150=0,"","/"&amp;TEXT(原表!N10/150,IF(MOD(原表!N10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>14/9.33%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="O13" s="24" t="str">
         <f>原表!O10&amp;IF(原表!O10/150=0,"","/"&amp;TEXT(原表!O10/150,IF(MOD(原表!O10/150,0.01)=0,"0%","0.00%")))</f>
@@ -1640,12 +1642,12 @@
       </c>
       <c r="P13" s="24" t="str">
         <f>原表!P10&amp;IF(原表!P10/150=0,"","/"&amp;TEXT(原表!P10/150,IF(MOD(原表!P10/150,0.01)=0,"0%","0.00%")))</f>
-        <v>41/27.33%</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="18" spans="2:16">
-      <c r="B14" s="9">
-        <v>2020</v>
+        <v>35/23.33%</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="18" spans="2:16">
+      <c r="B14" s="6">
+        <v>2021</v>
       </c>
       <c r="C14" s="24" t="str">
         <f>原表!C11&amp;IF(原表!C11/150=0,"","/"&amp;TEXT(原表!C11/150,IF(MOD(原表!C11/150,0.01)=0,"0%","0.00%")))</f>
@@ -1653,11 +1655,11 @@
       </c>
       <c r="D14" s="24" t="str">
         <f>原表!D11&amp;IF(原表!D11/150=0,"","/"&amp;TEXT(原表!D11/150,IF(MOD(原表!D11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>20/13.33%</v>
+        <v>15/10%</v>
       </c>
       <c r="E14" s="24" t="str">
         <f>原表!E11&amp;IF(原表!E11/150=0,"","/"&amp;TEXT(原表!E11/150,IF(MOD(原表!E11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>0</v>
       </c>
       <c r="F14" s="24" t="str">
         <f>原表!F11&amp;IF(原表!F11/150=0,"","/"&amp;TEXT(原表!F11/150,IF(MOD(原表!F11/150,0.01)=0,"0%","0.00%")))</f>
@@ -1665,56 +1667,56 @@
       </c>
       <c r="G14" s="24" t="str">
         <f>原表!G11&amp;IF(原表!G11/150=0,"","/"&amp;TEXT(原表!G11/150,IF(MOD(原表!G11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>5/3.33%</v>
       </c>
       <c r="H14" s="24" t="str">
         <f>原表!H11&amp;IF(原表!H11/150=0,"","/"&amp;TEXT(原表!H11/150,IF(MOD(原表!H11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>19/12.67%</v>
+        <v>15/10%</v>
       </c>
       <c r="I14" s="24" t="str">
         <f>原表!I11&amp;IF(原表!I11/150=0,"","/"&amp;TEXT(原表!I11/150,IF(MOD(原表!I11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>15/10%</v>
       </c>
       <c r="J14" s="24" t="str">
         <f>原表!J11&amp;IF(原表!J11/150=0,"","/"&amp;TEXT(原表!J11/150,IF(MOD(原表!J11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>16/10.67%</v>
+        <v>11/7.33%</v>
       </c>
       <c r="K14" s="24" t="str">
         <f>原表!K11&amp;IF(原表!K11/150=0,"","/"&amp;TEXT(原表!K11/150,IF(MOD(原表!K11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>49/32.67%</v>
+        <v>51/34%</v>
       </c>
       <c r="L14" s="24" t="str">
         <f>原表!L11&amp;IF(原表!L11/150=0,"","/"&amp;TEXT(原表!L11/150,IF(MOD(原表!L11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>11/7.33%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="M14" s="24" t="str">
         <f>原表!M11&amp;IF(原表!M11/150=0,"","/"&amp;TEXT(原表!M11/150,IF(MOD(原表!M11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>12/8%</v>
       </c>
       <c r="N14" s="24" t="str">
         <f>原表!N11&amp;IF(原表!N11/150=0,"","/"&amp;TEXT(原表!N11/150,IF(MOD(原表!N11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>14/9.33%</v>
       </c>
       <c r="O14" s="24" t="str">
         <f>原表!O11&amp;IF(原表!O11/150=0,"","/"&amp;TEXT(原表!O11/150,IF(MOD(原表!O11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>9/6%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="P14" s="24" t="str">
         <f>原表!P11&amp;IF(原表!P11/150=0,"","/"&amp;TEXT(原表!P11/150,IF(MOD(原表!P11/150,0.01)=0,"0%","0.00%")))</f>
-        <v>38/25.33%</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="18" spans="2:16">
-      <c r="B15" s="6">
-        <v>2019</v>
+        <v>41/27.33%</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="18" spans="2:16">
+      <c r="B15" s="9">
+        <v>2020</v>
       </c>
       <c r="C15" s="24" t="str">
         <f>原表!C12&amp;IF(原表!C12/150=0,"","/"&amp;TEXT(原表!C12/150,IF(MOD(原表!C12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>44/29.33%</v>
+        <v>43/28.67%</v>
       </c>
       <c r="D15" s="24" t="str">
         <f>原表!D12&amp;IF(原表!D12/150=0,"","/"&amp;TEXT(原表!D12/150,IF(MOD(原表!D12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>20/13.33%</v>
       </c>
       <c r="E15" s="24" t="str">
         <f>原表!E12&amp;IF(原表!E12/150=0,"","/"&amp;TEXT(原表!E12/150,IF(MOD(原表!E12/150,0.01)=0,"0%","0.00%")))</f>
@@ -1730,35 +1732,35 @@
       </c>
       <c r="H15" s="24" t="str">
         <f>原表!H12&amp;IF(原表!H12/150=0,"","/"&amp;TEXT(原表!H12/150,IF(MOD(原表!H12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>19/12.67%</v>
       </c>
       <c r="I15" s="24" t="str">
         <f>原表!I12&amp;IF(原表!I12/150=0,"","/"&amp;TEXT(原表!I12/150,IF(MOD(原表!I12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="J15" s="24" t="str">
         <f>原表!J12&amp;IF(原表!J12/150=0,"","/"&amp;TEXT(原表!J12/150,IF(MOD(原表!J12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>16/10.67%</v>
       </c>
       <c r="K15" s="24" t="str">
         <f>原表!K12&amp;IF(原表!K12/150=0,"","/"&amp;TEXT(原表!K12/150,IF(MOD(原表!K12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>50/33.33%</v>
+        <v>49/32.67%</v>
       </c>
       <c r="L15" s="24" t="str">
         <f>原表!L12&amp;IF(原表!L12/150=0,"","/"&amp;TEXT(原表!L12/150,IF(MOD(原表!L12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>11/7.33%</v>
       </c>
       <c r="M15" s="24" t="str">
         <f>原表!M12&amp;IF(原表!M12/150=0,"","/"&amp;TEXT(原表!M12/150,IF(MOD(原表!M12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>13/8.67%</v>
+        <v>18/12%</v>
       </c>
       <c r="N15" s="24" t="str">
         <f>原表!N12&amp;IF(原表!N12/150=0,"","/"&amp;TEXT(原表!N12/150,IF(MOD(原表!N12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>0</v>
       </c>
       <c r="O15" s="24" t="str">
         <f>原表!O12&amp;IF(原表!O12/150=0,"","/"&amp;TEXT(原表!O12/150,IF(MOD(原表!O12/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>9/6%</v>
       </c>
       <c r="P15" s="24" t="str">
         <f>原表!P12&amp;IF(原表!P12/150=0,"","/"&amp;TEXT(原表!P12/150,IF(MOD(原表!P12/150,0.01)=0,"0%","0.00%")))</f>
@@ -1767,43 +1769,43 @@
     </row>
     <row r="16" customFormat="1" ht="18" spans="2:16">
       <c r="B16" s="6">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C16" s="24" t="str">
         <f>原表!C13&amp;IF(原表!C13/150=0,"","/"&amp;TEXT(原表!C13/150,IF(MOD(原表!C13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>32/21.33%</v>
+        <v>44/29.33%</v>
       </c>
       <c r="D16" s="24" t="str">
         <f>原表!D13&amp;IF(原表!D13/150=0,"","/"&amp;TEXT(原表!D13/150,IF(MOD(原表!D13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>20/13.33%</v>
+        <v>18/12%</v>
       </c>
       <c r="E16" s="24" t="str">
         <f>原表!E13&amp;IF(原表!E13/150=0,"","/"&amp;TEXT(原表!E13/150,IF(MOD(原表!E13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="F16" s="24" t="str">
         <f>原表!F13&amp;IF(原表!F13/150=0,"","/"&amp;TEXT(原表!F13/150,IF(MOD(原表!F13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="G16" s="24" t="str">
         <f>原表!G13&amp;IF(原表!G13/150=0,"","/"&amp;TEXT(原表!G13/150,IF(MOD(原表!G13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>0</v>
       </c>
       <c r="H16" s="24" t="str">
         <f>原表!H13&amp;IF(原表!H13/150=0,"","/"&amp;TEXT(原表!H13/150,IF(MOD(原表!H13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>15/10%</v>
       </c>
       <c r="I16" s="24" t="str">
         <f>原表!I13&amp;IF(原表!I13/150=0,"","/"&amp;TEXT(原表!I13/150,IF(MOD(原表!I13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>15/10%</v>
       </c>
       <c r="J16" s="24" t="str">
         <f>原表!J13&amp;IF(原表!J13/150=0,"","/"&amp;TEXT(原表!J13/150,IF(MOD(原表!J13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>14/9.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="K16" s="24" t="str">
         <f>原表!K13&amp;IF(原表!K13/150=0,"","/"&amp;TEXT(原表!K13/150,IF(MOD(原表!K13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>48/32%</v>
+        <v>50/33.33%</v>
       </c>
       <c r="L16" s="24" t="str">
         <f>原表!L13&amp;IF(原表!L13/150=0,"","/"&amp;TEXT(原表!L13/150,IF(MOD(原表!L13/150,0.01)=0,"0%","0.00%")))</f>
@@ -1811,11 +1813,11 @@
       </c>
       <c r="M16" s="24" t="str">
         <f>原表!M13&amp;IF(原表!M13/150=0,"","/"&amp;TEXT(原表!M13/150,IF(MOD(原表!M13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>20/13.33%</v>
+        <v>13/8.67%</v>
       </c>
       <c r="N16" s="24" t="str">
         <f>原表!N13&amp;IF(原表!N13/150=0,"","/"&amp;TEXT(原表!N13/150,IF(MOD(原表!N13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="O16" s="24" t="str">
         <f>原表!O13&amp;IF(原表!O13/150=0,"","/"&amp;TEXT(原表!O13/150,IF(MOD(原表!O13/150,0.01)=0,"0%","0.00%")))</f>
@@ -1823,16 +1825,16 @@
       </c>
       <c r="P16" s="24" t="str">
         <f>原表!P13&amp;IF(原表!P13/150=0,"","/"&amp;TEXT(原表!P13/150,IF(MOD(原表!P13/150,0.01)=0,"0%","0.00%")))</f>
-        <v>50/33.33%</v>
+        <v>38/25.33%</v>
       </c>
     </row>
     <row r="17" customFormat="1" ht="18" spans="2:16">
       <c r="B17" s="6">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C17" s="24" t="str">
         <f>原表!C14&amp;IF(原表!C14/150=0,"","/"&amp;TEXT(原表!C14/150,IF(MOD(原表!C14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>47/31.33%</v>
+        <v>32/21.33%</v>
       </c>
       <c r="D17" s="24" t="str">
         <f>原表!D14&amp;IF(原表!D14/150=0,"","/"&amp;TEXT(原表!D14/150,IF(MOD(原表!D14/150,0.01)=0,"0%","0.00%")))</f>
@@ -1840,15 +1842,15 @@
       </c>
       <c r="E17" s="24" t="str">
         <f>原表!E14&amp;IF(原表!E14/150=0,"","/"&amp;TEXT(原表!E14/150,IF(MOD(原表!E14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="F17" s="24" t="str">
         <f>原表!F14&amp;IF(原表!F14/150=0,"","/"&amp;TEXT(原表!F14/150,IF(MOD(原表!F14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="G17" s="24" t="str">
         <f>原表!G14&amp;IF(原表!G14/150=0,"","/"&amp;TEXT(原表!G14/150,IF(MOD(原表!G14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>4/2.67%</v>
       </c>
       <c r="H17" s="24" t="str">
         <f>原表!H14&amp;IF(原表!H14/150=0,"","/"&amp;TEXT(原表!H14/150,IF(MOD(原表!H14/150,0.01)=0,"0%","0.00%")))</f>
@@ -1856,15 +1858,15 @@
       </c>
       <c r="I17" s="24" t="str">
         <f>原表!I14&amp;IF(原表!I14/150=0,"","/"&amp;TEXT(原表!I14/150,IF(MOD(原表!I14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>9/6%</v>
+        <v>18/12%</v>
       </c>
       <c r="J17" s="24" t="str">
         <f>原表!J14&amp;IF(原表!J14/150=0,"","/"&amp;TEXT(原表!J14/150,IF(MOD(原表!J14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>17/11.33%</v>
+        <v>14/9.33%</v>
       </c>
       <c r="K17" s="24" t="str">
         <f>原表!K14&amp;IF(原表!K14/150=0,"","/"&amp;TEXT(原表!K14/150,IF(MOD(原表!K14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>40/26.67%</v>
+        <v>48/32%</v>
       </c>
       <c r="L17" s="24" t="str">
         <f>原表!L14&amp;IF(原表!L14/150=0,"","/"&amp;TEXT(原表!L14/150,IF(MOD(原表!L14/150,0.01)=0,"0%","0.00%")))</f>
@@ -1872,11 +1874,11 @@
       </c>
       <c r="M17" s="24" t="str">
         <f>原表!M14&amp;IF(原表!M14/150=0,"","/"&amp;TEXT(原表!M14/150,IF(MOD(原表!M14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>18/12%</v>
+        <v>20/13.33%</v>
       </c>
       <c r="N17" s="24" t="str">
         <f>原表!N14&amp;IF(原表!N14/150=0,"","/"&amp;TEXT(原表!N14/150,IF(MOD(原表!N14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5/3.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="O17" s="24" t="str">
         <f>原表!O14&amp;IF(原表!O14/150=0,"","/"&amp;TEXT(原表!O14/150,IF(MOD(原表!O14/150,0.01)=0,"0%","0.00%")))</f>
@@ -1884,16 +1886,16 @@
       </c>
       <c r="P17" s="24" t="str">
         <f>原表!P14&amp;IF(原表!P14/150=0,"","/"&amp;TEXT(原表!P14/150,IF(MOD(原表!P14/150,0.01)=0,"0%","0.00%")))</f>
-        <v>43/28.67%</v>
+        <v>50/33.33%</v>
       </c>
     </row>
     <row r="18" customFormat="1" ht="18" spans="2:16">
       <c r="B18" s="6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C18" s="24" t="str">
         <f>原表!C15&amp;IF(原表!C15/150=0,"","/"&amp;TEXT(原表!C15/150,IF(MOD(原表!C15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>54/36%</v>
+        <v>47/31.33%</v>
       </c>
       <c r="D18" s="24" t="str">
         <f>原表!D15&amp;IF(原表!D15/150=0,"","/"&amp;TEXT(原表!D15/150,IF(MOD(原表!D15/150,0.01)=0,"0%","0.00%")))</f>
@@ -1901,7 +1903,7 @@
       </c>
       <c r="E18" s="24" t="str">
         <f>原表!E15&amp;IF(原表!E15/150=0,"","/"&amp;TEXT(原表!E15/150,IF(MOD(原表!E15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>0</v>
+        <v>5/3.33%</v>
       </c>
       <c r="F18" s="24" t="str">
         <f>原表!F15&amp;IF(原表!F15/150=0,"","/"&amp;TEXT(原表!F15/150,IF(MOD(原表!F15/150,0.01)=0,"0%","0.00%")))</f>
@@ -1913,15 +1915,15 @@
       </c>
       <c r="H18" s="24" t="str">
         <f>原表!H15&amp;IF(原表!H15/150=0,"","/"&amp;TEXT(原表!H15/150,IF(MOD(原表!H15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
+        <v>4/2.67%</v>
       </c>
       <c r="I18" s="24" t="str">
         <f>原表!I15&amp;IF(原表!I15/150=0,"","/"&amp;TEXT(原表!I15/150,IF(MOD(原表!I15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>9/6%</v>
       </c>
       <c r="J18" s="24" t="str">
         <f>原表!J15&amp;IF(原表!J15/150=0,"","/"&amp;TEXT(原表!J15/150,IF(MOD(原表!J15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>17/11.33%</v>
       </c>
       <c r="K18" s="24" t="str">
         <f>原表!K15&amp;IF(原表!K15/150=0,"","/"&amp;TEXT(原表!K15/150,IF(MOD(原表!K15/150,0.01)=0,"0%","0.00%")))</f>
@@ -1933,7 +1935,7 @@
       </c>
       <c r="M18" s="24" t="str">
         <f>原表!M15&amp;IF(原表!M15/150=0,"","/"&amp;TEXT(原表!M15/150,IF(MOD(原表!M15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>13/8.67%</v>
+        <v>18/12%</v>
       </c>
       <c r="N18" s="24" t="str">
         <f>原表!N15&amp;IF(原表!N15/150=0,"","/"&amp;TEXT(原表!N15/150,IF(MOD(原表!N15/150,0.01)=0,"0%","0.00%")))</f>
@@ -1941,20 +1943,20 @@
       </c>
       <c r="O18" s="24" t="str">
         <f>原表!O15&amp;IF(原表!O15/150=0,"","/"&amp;TEXT(原表!O15/150,IF(MOD(原表!O15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>8/5.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="P18" s="24" t="str">
         <f>原表!P15&amp;IF(原表!P15/150=0,"","/"&amp;TEXT(原表!P15/150,IF(MOD(原表!P15/150,0.01)=0,"0%","0.00%")))</f>
-        <v>36/24%</v>
+        <v>43/28.67%</v>
       </c>
     </row>
     <row r="19" customFormat="1" ht="18" spans="2:16">
       <c r="B19" s="6">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C19" s="24" t="str">
         <f>原表!C16&amp;IF(原表!C16/150=0,"","/"&amp;TEXT(原表!C16/150,IF(MOD(原表!C16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>32/21.33%</v>
+        <v>54/36%</v>
       </c>
       <c r="D19" s="24" t="str">
         <f>原表!D16&amp;IF(原表!D16/150=0,"","/"&amp;TEXT(原表!D16/150,IF(MOD(原表!D16/150,0.01)=0,"0%","0.00%")))</f>
@@ -1962,11 +1964,11 @@
       </c>
       <c r="E19" s="24" t="str">
         <f>原表!E16&amp;IF(原表!E16/150=0,"","/"&amp;TEXT(原表!E16/150,IF(MOD(原表!E16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>0</v>
       </c>
       <c r="F19" s="24" t="str">
         <f>原表!F16&amp;IF(原表!F16/150=0,"","/"&amp;TEXT(原表!F16/150,IF(MOD(原表!F16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="G19" s="24" t="str">
         <f>原表!G16&amp;IF(原表!G16/150=0,"","/"&amp;TEXT(原表!G16/150,IF(MOD(原表!G16/150,0.01)=0,"0%","0.00%")))</f>
@@ -1974,19 +1976,19 @@
       </c>
       <c r="H19" s="24" t="str">
         <f>原表!H16&amp;IF(原表!H16/150=0,"","/"&amp;TEXT(原表!H16/150,IF(MOD(原表!H16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>12/8%</v>
+        <v>15/10%</v>
       </c>
       <c r="I19" s="24" t="str">
         <f>原表!I16&amp;IF(原表!I16/150=0,"","/"&amp;TEXT(原表!I16/150,IF(MOD(原表!I16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>14/9.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="J19" s="24" t="str">
         <f>原表!J16&amp;IF(原表!J16/150=0,"","/"&amp;TEXT(原表!J16/150,IF(MOD(原表!J16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>14/9.33%</v>
+        <v>10/6.67%</v>
       </c>
       <c r="K19" s="24" t="str">
         <f>原表!K16&amp;IF(原表!K16/150=0,"","/"&amp;TEXT(原表!K16/150,IF(MOD(原表!K16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>48/32%</v>
+        <v>40/26.67%</v>
       </c>
       <c r="L19" s="24" t="str">
         <f>原表!L16&amp;IF(原表!L16/150=0,"","/"&amp;TEXT(原表!L16/150,IF(MOD(原表!L16/150,0.01)=0,"0%","0.00%")))</f>
@@ -1994,98 +1996,142 @@
       </c>
       <c r="M19" s="24" t="str">
         <f>原表!M16&amp;IF(原表!M16/150=0,"","/"&amp;TEXT(原表!M16/150,IF(MOD(原表!M16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>26/17.33%</v>
+        <v>13/8.67%</v>
       </c>
       <c r="N19" s="24" t="str">
         <f>原表!N16&amp;IF(原表!N16/150=0,"","/"&amp;TEXT(原表!N16/150,IF(MOD(原表!N16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>4/2.67%</v>
+        <v>5/3.33%</v>
       </c>
       <c r="O19" s="24" t="str">
         <f>原表!O16&amp;IF(原表!O16/150=0,"","/"&amp;TEXT(原表!O16/150,IF(MOD(原表!O16/150,0.01)=0,"0%","0.00%")))</f>
-        <v>10/6.67%</v>
+        <v>8/5.33%</v>
       </c>
       <c r="P19" s="24" t="str">
         <f>原表!P16&amp;IF(原表!P16/150=0,"","/"&amp;TEXT(原表!P16/150,IF(MOD(原表!P16/150,0.01)=0,"0%","0.00%")))</f>
+        <v>36/24%</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="18" spans="2:16">
+      <c r="B20" s="6">
+        <v>2015</v>
+      </c>
+      <c r="C20" s="24" t="str">
+        <f>原表!C17&amp;IF(原表!C17/150=0,"","/"&amp;TEXT(原表!C17/150,IF(MOD(原表!C17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>32/21.33%</v>
+      </c>
+      <c r="D20" s="24" t="str">
+        <f>原表!D17&amp;IF(原表!D17/150=0,"","/"&amp;TEXT(原表!D17/150,IF(MOD(原表!D17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>20/13.33%</v>
+      </c>
+      <c r="E20" s="24" t="str">
+        <f>原表!E17&amp;IF(原表!E17/150=0,"","/"&amp;TEXT(原表!E17/150,IF(MOD(原表!E17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>4/2.67%</v>
+      </c>
+      <c r="F20" s="24" t="str">
+        <f>原表!F17&amp;IF(原表!F17/150=0,"","/"&amp;TEXT(原表!F17/150,IF(MOD(原表!F17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>4/2.67%</v>
+      </c>
+      <c r="G20" s="24" t="str">
+        <f>原表!G17&amp;IF(原表!G17/150=0,"","/"&amp;TEXT(原表!G17/150,IF(MOD(原表!G17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="24" t="str">
+        <f>原表!H17&amp;IF(原表!H17/150=0,"","/"&amp;TEXT(原表!H17/150,IF(MOD(原表!H17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>12/8%</v>
+      </c>
+      <c r="I20" s="24" t="str">
+        <f>原表!I17&amp;IF(原表!I17/150=0,"","/"&amp;TEXT(原表!I17/150,IF(MOD(原表!I17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>14/9.33%</v>
+      </c>
+      <c r="J20" s="24" t="str">
+        <f>原表!J17&amp;IF(原表!J17/150=0,"","/"&amp;TEXT(原表!J17/150,IF(MOD(原表!J17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>14/9.33%</v>
+      </c>
+      <c r="K20" s="24" t="str">
+        <f>原表!K17&amp;IF(原表!K17/150=0,"","/"&amp;TEXT(原表!K17/150,IF(MOD(原表!K17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>48/32%</v>
+      </c>
+      <c r="L20" s="24" t="str">
+        <f>原表!L17&amp;IF(原表!L17/150=0,"","/"&amp;TEXT(原表!L17/150,IF(MOD(原表!L17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>10/6.67%</v>
+      </c>
+      <c r="M20" s="24" t="str">
+        <f>原表!M17&amp;IF(原表!M17/150=0,"","/"&amp;TEXT(原表!M17/150,IF(MOD(原表!M17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>26/17.33%</v>
+      </c>
+      <c r="N20" s="24" t="str">
+        <f>原表!N17&amp;IF(原表!N17/150=0,"","/"&amp;TEXT(原表!N17/150,IF(MOD(原表!N17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>4/2.67%</v>
+      </c>
+      <c r="O20" s="24" t="str">
+        <f>原表!O17&amp;IF(原表!O17/150=0,"","/"&amp;TEXT(原表!O17/150,IF(MOD(原表!O17/150,0.01)=0,"0%","0.00%")))</f>
+        <v>10/6.67%</v>
+      </c>
+      <c r="P20" s="24" t="str">
+        <f>原表!P17&amp;IF(原表!P17/150=0,"","/"&amp;TEXT(原表!P17/150,IF(MOD(原表!P17/150,0.01)=0,"0%","0.00%")))</f>
         <v>50/33.33%</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="18" spans="2:16">
-      <c r="B20" s="6" t="s">
+    <row r="21" customFormat="1" ht="18" spans="2:16">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="24" t="str">
-        <f>原表!C18&amp;IF(原表!C18/150=0,"","/"&amp;TEXT(原表!C18/150,IF(MOD(原表!C18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>42.73/28.49%</v>
-      </c>
-      <c r="D20" s="24" t="str">
-        <f>原表!D18&amp;IF(原表!D18/150=0,"","/"&amp;TEXT(原表!D18/150,IF(MOD(原表!D18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>17.91/11.94%</v>
-      </c>
-      <c r="E20" s="24" t="str">
-        <f>原表!E18&amp;IF(原表!E18/150=0,"","/"&amp;TEXT(原表!E18/150,IF(MOD(原表!E18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>2.91/1.94%</v>
-      </c>
-      <c r="F20" s="24" t="str">
-        <f>原表!F18&amp;IF(原表!F18/150=0,"","/"&amp;TEXT(原表!F18/150,IF(MOD(原表!F18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>3.82/2.55%</v>
-      </c>
-      <c r="G20" s="24" t="str">
-        <f>原表!G18&amp;IF(原表!G18/150=0,"","/"&amp;TEXT(原表!G18/150,IF(MOD(原表!G18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>2/1.33%</v>
-      </c>
-      <c r="H20" s="24" t="str">
-        <f>原表!H18&amp;IF(原表!H18/150=0,"","/"&amp;TEXT(原表!H18/150,IF(MOD(原表!H18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15.55/10.37%</v>
-      </c>
-      <c r="I20" s="24" t="str">
-        <f>原表!I18&amp;IF(原表!I18/150=0,"","/"&amp;TEXT(原表!I18/150,IF(MOD(原表!I18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>11.45/7.63%</v>
-      </c>
-      <c r="J20" s="24" t="str">
-        <f>原表!J18&amp;IF(原表!J18/150=0,"","/"&amp;TEXT(原表!J18/150,IF(MOD(原表!J18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>13.82/9.21%</v>
-      </c>
-      <c r="K20" s="24" t="str">
-        <f>原表!K18&amp;IF(原表!K18/150=0,"","/"&amp;TEXT(原表!K18/150,IF(MOD(原表!K18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>49.55/33.03%</v>
-      </c>
-      <c r="L20" s="24" t="str">
-        <f>原表!L18&amp;IF(原表!L18/150=0,"","/"&amp;TEXT(原表!L18/150,IF(MOD(原表!L18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>9.64/6.43%</v>
-      </c>
-      <c r="M20" s="24" t="str">
-        <f>原表!M18&amp;IF(原表!M18/150=0,"","/"&amp;TEXT(原表!M18/150,IF(MOD(原表!M18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>15/10%</v>
-      </c>
-      <c r="N20" s="24" t="str">
-        <f>原表!N18&amp;IF(原表!N18/150=0,"","/"&amp;TEXT(原表!N18/150,IF(MOD(原表!N18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>5.45/3.63%</v>
-      </c>
-      <c r="O20" s="24" t="str">
-        <f>原表!O18&amp;IF(原表!O18/150=0,"","/"&amp;TEXT(原表!O18/150,IF(MOD(原表!O18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>9.73/6.49%</v>
-      </c>
-      <c r="P20" s="24" t="str">
-        <f>原表!P18&amp;IF(原表!P18/150=0,"","/"&amp;TEXT(原表!P18/150,IF(MOD(原表!P18/150,0.01)=0,"0%","0.00%")))</f>
-        <v>39.82/26.55%</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" ht="14" customHeight="1" spans="2:16">
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
+      <c r="C21" s="24" t="str">
+        <f>原表!C19&amp;IF(原表!C19/150=0,"","/"&amp;TEXT(原表!C19/150,IF(MOD(原表!C19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>43/28.67%</v>
+      </c>
+      <c r="D21" s="24" t="str">
+        <f>原表!D19&amp;IF(原表!D19/150=0,"","/"&amp;TEXT(原表!D19/150,IF(MOD(原表!D19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>18.08/12.05%</v>
+      </c>
+      <c r="E21" s="24" t="str">
+        <f>原表!E19&amp;IF(原表!E19/150=0,"","/"&amp;TEXT(原表!E19/150,IF(MOD(原表!E19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>2.67/1.78%</v>
+      </c>
+      <c r="F21" s="24" t="str">
+        <f>原表!F19&amp;IF(原表!F19/150=0,"","/"&amp;TEXT(原表!F19/150,IF(MOD(原表!F19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>3.83/2.55%</v>
+      </c>
+      <c r="G21" s="24" t="str">
+        <f>原表!G19&amp;IF(原表!G19/150=0,"","/"&amp;TEXT(原表!G19/150,IF(MOD(原表!G19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>1.83/1.22%</v>
+      </c>
+      <c r="H21" s="24" t="str">
+        <f>原表!H19&amp;IF(原表!H19/150=0,"","/"&amp;TEXT(原表!H19/150,IF(MOD(原表!H19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>16.25/10.83%</v>
+      </c>
+      <c r="I21" s="24" t="str">
+        <f>原表!I19&amp;IF(原表!I19/150=0,"","/"&amp;TEXT(原表!I19/150,IF(MOD(原表!I19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>11.25/7.50%</v>
+      </c>
+      <c r="J21" s="24" t="str">
+        <f>原表!J19&amp;IF(原表!J19/150=0,"","/"&amp;TEXT(原表!J19/150,IF(MOD(原表!J19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>14.25/9.50%</v>
+      </c>
+      <c r="K21" s="24" t="str">
+        <f>原表!K19&amp;IF(原表!K19/150=0,"","/"&amp;TEXT(原表!K19/150,IF(MOD(原表!K19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>50.08/33.39%</v>
+      </c>
+      <c r="L21" s="24" t="str">
+        <f>原表!L19&amp;IF(原表!L19/150=0,"","/"&amp;TEXT(原表!L19/150,IF(MOD(原表!L19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>8.83/5.89%</v>
+      </c>
+      <c r="M21" s="24" t="str">
+        <f>原表!M19&amp;IF(原表!M19/150=0,"","/"&amp;TEXT(原表!M19/150,IF(MOD(原表!M19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>14.92/9.95%</v>
+      </c>
+      <c r="N21" s="24" t="str">
+        <f>原表!N19&amp;IF(原表!N19/150=0,"","/"&amp;TEXT(原表!N19/150,IF(MOD(原表!N19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>5.33/3.55%</v>
+      </c>
+      <c r="O21" s="24" t="str">
+        <f>原表!O19&amp;IF(原表!O19/150=0,"","/"&amp;TEXT(原表!O19/150,IF(MOD(原表!O19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>9.75/6.50%</v>
+      </c>
+      <c r="P21" s="24" t="str">
+        <f>原表!P19&amp;IF(原表!P19/150=0,"","/"&amp;TEXT(原表!P19/150,IF(MOD(原表!P19/150,0.01)=0,"0%","0.00%")))</f>
+        <v>38.83/25.89%</v>
+      </c>
     </row>
     <row r="22" customFormat="1" ht="14" customHeight="1" spans="2:16">
       <c r="B22" s="11"/>
@@ -2189,35 +2235,38 @@
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
-    <row r="28" customFormat="1" ht="14" customHeight="1" spans="2:2">
+    <row r="28" customFormat="1" ht="14" customHeight="1" spans="2:16">
       <c r="B28" s="11"/>
-    </row>
-    <row r="29" customFormat="1" ht="14" customHeight="1" spans="2:15">
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+    </row>
+    <row r="29" customFormat="1" ht="14" customHeight="1" spans="2:2">
       <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="F29" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-    </row>
-    <row r="30" customFormat="1" ht="16" customHeight="1" spans="2:15">
+    </row>
+    <row r="30" customFormat="1" ht="14" customHeight="1" spans="2:15">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="21"/>
+      <c r="F30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="20"/>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="19"/>
@@ -2236,7 +2285,7 @@
       <c r="N31" s="19"/>
       <c r="O31" s="19"/>
     </row>
-    <row r="32" customFormat="1" ht="16" customHeight="1" spans="2:12">
+    <row r="32" customFormat="1" ht="16" customHeight="1" spans="2:15">
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="F32" s="15"/>
@@ -2246,31 +2295,45 @@
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
       <c r="L32" s="21"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
     </row>
     <row r="33" customFormat="1" ht="16" customHeight="1" spans="2:12">
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="22"/>
-    </row>
-    <row r="34" customFormat="1" ht="16" customHeight="1" spans="2:3">
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" customFormat="1" ht="16" customHeight="1" spans="2:12">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
-    </row>
-    <row r="35" customFormat="1" ht="14" customHeight="1" spans="2:3">
+      <c r="F34" s="17"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" customFormat="1" ht="16" customHeight="1" spans="2:3">
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
     </row>
-    <row r="36" customFormat="1" ht="14" customHeight="1" spans="2:2">
+    <row r="36" customFormat="1" ht="14" customHeight="1" spans="2:3">
       <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
     </row>
     <row r="37" customFormat="1" ht="14" customHeight="1" spans="2:2">
       <c r="B37" s="11"/>
+    </row>
+    <row r="38" customFormat="1" ht="14" customHeight="1" spans="2:2">
+      <c r="B38" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2279,7 +2342,7 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F29:L33"/>
+    <mergeCell ref="F30:L34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape"/>
@@ -2290,7 +2353,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B4:Q30"/>
+  <dimension ref="B4:Q31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="15.625" customWidth="1"/>
@@ -2384,51 +2447,51 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="2:17">
       <c r="B6" s="6">
-        <v>2025</v>
-      </c>
-      <c r="C6" s="6">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="4">
         <v>46</v>
       </c>
-      <c r="D6" s="7">
-        <v>16</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="D6" s="4">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
         <v>4</v>
       </c>
-      <c r="G6" s="7">
-        <v>4</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
         <v>24</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <v>9</v>
       </c>
-      <c r="J6" s="7">
-        <v>15</v>
+      <c r="J6" s="4">
+        <v>19</v>
       </c>
       <c r="K6" s="7">
         <f>SUM(E6:J6)</f>
         <v>56</v>
       </c>
-      <c r="L6" s="7">
-        <v>8</v>
-      </c>
-      <c r="M6" s="7">
-        <v>10</v>
-      </c>
-      <c r="N6" s="7">
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>14</v>
+      </c>
+      <c r="N6" s="4">
         <v>4</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="4">
         <v>10</v>
       </c>
       <c r="P6" s="7">
         <f>SUM(L6:O6)</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q6" s="23">
         <f>SUM(C6:J6,L6:O6)</f>
@@ -2437,25 +2500,25 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="2:17">
       <c r="B7" s="6">
-        <v>2024</v>
-      </c>
-      <c r="C7" s="8">
-        <v>42</v>
+        <v>2025</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46</v>
       </c>
       <c r="D7" s="7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
         <v>4</v>
       </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
       <c r="G7" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I7" s="7">
         <v>9</v>
@@ -2464,14 +2527,14 @@
         <v>15</v>
       </c>
       <c r="K7" s="7">
-        <f t="shared" ref="K7:K16" si="0">SUM(E7:J7)</f>
+        <f>SUM(E7:J7)</f>
         <v>56</v>
       </c>
       <c r="L7" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M7" s="7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N7" s="7">
         <v>4</v>
@@ -2480,114 +2543,114 @@
         <v>10</v>
       </c>
       <c r="P7" s="7">
-        <f t="shared" ref="P7:P16" si="1">SUM(L7:O7)</f>
-        <v>34</v>
+        <f>SUM(L7:O7)</f>
+        <v>32</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" ref="Q7:Q16" si="2">SUM(C7:J7,L7:O7)</f>
+        <f>SUM(C7:J7,L7:O7)</f>
         <v>150</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="2:17">
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="2:17">
       <c r="B8" s="6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" s="8">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="7">
         <v>0</v>
       </c>
       <c r="G8" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I8" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J8" s="7">
         <v>15</v>
       </c>
       <c r="K8" s="7">
+        <f t="shared" ref="K8:K17" si="0">SUM(E8:J8)</f>
+        <v>56</v>
+      </c>
+      <c r="L8" s="7">
+        <v>4</v>
+      </c>
+      <c r="M8" s="7">
+        <v>16</v>
+      </c>
+      <c r="N8" s="7">
+        <v>4</v>
+      </c>
+      <c r="O8" s="7">
+        <v>10</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" ref="P8:P17" si="1">SUM(L8:O8)</f>
+        <v>34</v>
+      </c>
+      <c r="Q8" s="23">
+        <f t="shared" ref="Q8:Q17" si="2">SUM(C8:J8,L8:O8)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="2:17">
+      <c r="B9" s="6">
+        <v>2023</v>
+      </c>
+      <c r="C9" s="8">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4</v>
+      </c>
+      <c r="H9" s="7">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7">
+        <v>13</v>
+      </c>
+      <c r="J9" s="7">
+        <v>15</v>
+      </c>
+      <c r="K9" s="7">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L9" s="7">
         <v>18</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M9" s="7">
         <v>9</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N9" s="7">
         <v>4</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O9" s="7">
         <v>10</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P9" s="7">
         <f t="shared" si="1"/>
         <v>41</v>
-      </c>
-      <c r="Q8" s="23">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" ht="18" spans="2:17">
-      <c r="B9" s="6">
-        <v>2022</v>
-      </c>
-      <c r="C9" s="8">
-        <v>44</v>
-      </c>
-      <c r="D9" s="7">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>5</v>
-      </c>
-      <c r="G9" s="7">
-        <v>5</v>
-      </c>
-      <c r="H9" s="7">
-        <v>16</v>
-      </c>
-      <c r="I9" s="7">
-        <v>10</v>
-      </c>
-      <c r="J9" s="7">
-        <v>15</v>
-      </c>
-      <c r="K9" s="7">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="L9" s="7">
-        <v>10</v>
-      </c>
-      <c r="M9" s="7">
-        <v>10</v>
-      </c>
-      <c r="N9" s="7">
-        <v>5</v>
-      </c>
-      <c r="O9" s="7">
-        <v>10</v>
-      </c>
-      <c r="P9" s="7">
-        <f t="shared" si="1"/>
-        <v>35</v>
       </c>
       <c r="Q9" s="23">
         <f t="shared" si="2"/>
@@ -2596,16 +2659,16 @@
     </row>
     <row r="10" ht="18" spans="2:17">
       <c r="B10" s="6">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C10" s="8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="7">
         <v>15</v>
       </c>
       <c r="E10" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="7">
         <v>5</v>
@@ -2614,101 +2677,101 @@
         <v>5</v>
       </c>
       <c r="H10" s="7">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7">
+        <v>10</v>
+      </c>
+      <c r="J10" s="7">
         <v>15</v>
-      </c>
-      <c r="I10" s="7">
-        <v>15</v>
-      </c>
-      <c r="J10" s="7">
-        <v>11</v>
       </c>
       <c r="K10" s="7">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L10" s="7">
+        <v>10</v>
+      </c>
+      <c r="M10" s="7">
+        <v>10</v>
+      </c>
+      <c r="N10" s="7">
         <v>5</v>
-      </c>
-      <c r="M10" s="7">
-        <v>12</v>
-      </c>
-      <c r="N10" s="7">
-        <v>14</v>
       </c>
       <c r="O10" s="7">
         <v>10</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q10" s="23">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="18" spans="2:17">
-      <c r="B11" s="9">
-        <v>2020</v>
+    <row r="11" ht="18" spans="2:17">
+      <c r="B11" s="6">
+        <v>2021</v>
       </c>
       <c r="C11" s="8">
         <v>43</v>
       </c>
       <c r="D11" s="7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" s="7">
         <v>5</v>
       </c>
       <c r="G11" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I11" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J11" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L11" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M11" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N11" s="7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O11" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q11" s="23">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
     </row>
-    <row r="12" ht="18" spans="2:17">
-      <c r="B12" s="6">
-        <v>2019</v>
+    <row r="12" s="2" customFormat="1" ht="18" spans="2:17">
+      <c r="B12" s="9">
+        <v>2020</v>
       </c>
       <c r="C12" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7">
         <v>5</v>
@@ -2720,29 +2783,29 @@
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I12" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J12" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L12" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N12" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="1"/>
@@ -2755,51 +2818,51 @@
     </row>
     <row r="13" ht="18" spans="2:17">
       <c r="B13" s="6">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C13" s="8">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J13" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K13" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L13" s="7">
         <v>10</v>
       </c>
       <c r="M13" s="7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N13" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O13" s="7">
         <v>10</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="2"/>
@@ -2808,51 +2871,51 @@
     </row>
     <row r="14" ht="18" spans="2:17">
       <c r="B14" s="6">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C14" s="8">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7">
         <v>20</v>
       </c>
       <c r="E14" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
       </c>
       <c r="I14" s="7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J14" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K14" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L14" s="7">
         <v>10</v>
       </c>
       <c r="M14" s="7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N14" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O14" s="7">
         <v>10</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="2"/>
@@ -2861,16 +2924,16 @@
     </row>
     <row r="15" ht="18" spans="2:17">
       <c r="B15" s="6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C15" s="8">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D15" s="7">
         <v>20</v>
       </c>
       <c r="E15" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15" s="7">
         <v>5</v>
@@ -2879,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="0"/>
@@ -2895,17 +2958,17 @@
         <v>10</v>
       </c>
       <c r="M15" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N15" s="7">
         <v>5</v>
       </c>
       <c r="O15" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="2"/>
@@ -2914,93 +2977,94 @@
     </row>
     <row r="16" ht="18" spans="2:17">
       <c r="B16" s="6">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C16" s="8">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D16" s="7">
         <v>20</v>
       </c>
       <c r="E16" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="7">
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I16" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J16" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L16" s="7">
         <v>10</v>
       </c>
       <c r="M16" s="7">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="N16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
     </row>
-    <row r="17" ht="18" hidden="1" spans="2:17">
-      <c r="B17" s="6" t="s">
-        <v>19</v>
+    <row r="17" ht="18" spans="2:17">
+      <c r="B17" s="6">
+        <v>2015</v>
       </c>
       <c r="C17" s="8">
-        <v>42.4</v>
+        <v>32</v>
       </c>
       <c r="D17" s="7">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="E17" s="7">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G17" s="7">
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I17" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J17" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K17" s="7">
-        <v>56</v>
+        <f t="shared" si="0"/>
+        <v>48</v>
       </c>
       <c r="L17" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M17" s="7">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N17" s="7">
         <v>4</v>
@@ -3008,94 +3072,129 @@
       <c r="O17" s="7">
         <v>10</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="7">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="Q17" s="23">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" ht="18" hidden="1" spans="2:17">
+      <c r="B18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="8">
+        <v>42.4</v>
+      </c>
+      <c r="D18" s="7">
+        <v>18.1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>28</v>
+      </c>
+      <c r="I18" s="7">
+        <v>9</v>
+      </c>
+      <c r="J18" s="7">
+        <v>15</v>
+      </c>
+      <c r="K18" s="7">
+        <v>56</v>
+      </c>
+      <c r="L18" s="7">
+        <v>4</v>
+      </c>
+      <c r="M18" s="7">
+        <v>16</v>
+      </c>
+      <c r="N18" s="7">
+        <v>4</v>
+      </c>
+      <c r="O18" s="7">
+        <v>10</v>
+      </c>
+      <c r="P18" s="8">
         <v>40</v>
       </c>
-      <c r="Q17" s="23"/>
-    </row>
-    <row r="18" ht="18" spans="2:17">
-      <c r="B18" s="6" t="s">
+      <c r="Q18" s="23"/>
+    </row>
+    <row r="19" ht="18" spans="2:17">
+      <c r="B19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="10">
-        <f t="shared" ref="C18:P18" si="3">ROUND(AVERAGE(C6:C16),2)</f>
-        <v>42.73</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C19" s="10">
+        <f>ROUND(AVERAGE(C6:C17),2)</f>
+        <v>43</v>
+      </c>
+      <c r="D19" s="10">
+        <f t="shared" ref="D19:Q19" si="3">ROUND(AVERAGE(D6:D17),2)</f>
+        <v>18.08</v>
+      </c>
+      <c r="E19" s="10">
         <f t="shared" si="3"/>
-        <v>17.91</v>
-      </c>
-      <c r="E18" s="10">
+        <v>2.67</v>
+      </c>
+      <c r="F19" s="10">
         <f t="shared" si="3"/>
-        <v>2.91</v>
-      </c>
-      <c r="F18" s="10">
+        <v>3.83</v>
+      </c>
+      <c r="G19" s="10">
         <f t="shared" si="3"/>
-        <v>3.82</v>
-      </c>
-      <c r="G18" s="10">
+        <v>1.83</v>
+      </c>
+      <c r="H19" s="10">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="H18" s="10">
+        <v>16.25</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="3"/>
-        <v>15.55</v>
-      </c>
-      <c r="I18" s="10">
+        <v>11.25</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="3"/>
-        <v>11.45</v>
-      </c>
-      <c r="J18" s="10">
+        <v>14.25</v>
+      </c>
+      <c r="K19" s="10">
         <f t="shared" si="3"/>
-        <v>13.82</v>
-      </c>
-      <c r="K18" s="10">
+        <v>50.08</v>
+      </c>
+      <c r="L19" s="10">
         <f t="shared" si="3"/>
-        <v>49.55</v>
-      </c>
-      <c r="L18" s="10">
+        <v>8.83</v>
+      </c>
+      <c r="M19" s="10">
         <f t="shared" si="3"/>
-        <v>9.64</v>
-      </c>
-      <c r="M18" s="10">
+        <v>14.92</v>
+      </c>
+      <c r="N19" s="10">
         <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="N18" s="10">
+        <v>5.33</v>
+      </c>
+      <c r="O19" s="10">
         <f t="shared" si="3"/>
-        <v>5.45</v>
-      </c>
-      <c r="O18" s="10">
+        <v>9.75</v>
+      </c>
+      <c r="P19" s="10">
         <f t="shared" si="3"/>
-        <v>9.73</v>
-      </c>
-      <c r="P18" s="10">
+        <v>38.83</v>
+      </c>
+      <c r="Q19" s="10">
         <f t="shared" si="3"/>
-        <v>39.82</v>
-      </c>
-      <c r="Q18" s="23">
-        <f>SUM(C18:J18,L18:O18)</f>
-        <v>150.01</v>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1" spans="2:16">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-    </row>
-    <row r="20" customFormat="1" ht="14" customHeight="1" spans="2:12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="2:16">
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3107,8 +3206,12 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
-    </row>
-    <row r="21" customFormat="1" ht="14" customHeight="1" spans="2:15">
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+    </row>
+    <row r="21" customFormat="1" ht="14" customHeight="1" spans="2:12">
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3120,11 +3223,8 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-    </row>
-    <row r="22" customFormat="1" ht="16" customHeight="1" spans="2:15">
+    </row>
+    <row r="22" customFormat="1" ht="14" customHeight="1" spans="2:15">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3156,7 +3256,7 @@
       <c r="N23" s="19"/>
       <c r="O23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="16" customHeight="1" spans="2:12">
+    <row r="24" customFormat="1" ht="16" customHeight="1" spans="2:15">
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -3168,35 +3268,38 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
-    </row>
-    <row r="25" customFormat="1" ht="16" customHeight="1" spans="2:2">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+    </row>
+    <row r="25" customFormat="1" ht="16" customHeight="1" spans="2:12">
       <c r="B25" s="11"/>
-    </row>
-    <row r="26" customFormat="1" ht="16" customHeight="1" spans="2:12">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" customFormat="1" ht="16" customHeight="1" spans="2:2">
       <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="20"/>
-    </row>
-    <row r="27" customFormat="1" ht="14" customHeight="1" spans="2:12">
+    </row>
+    <row r="27" customFormat="1" ht="16" customHeight="1" spans="2:12">
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="21"/>
+      <c r="F27" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" customFormat="1" ht="14" customHeight="1" spans="2:12">
       <c r="B28" s="11"/>
@@ -3220,16 +3323,27 @@
       <c r="K29" s="16"/>
       <c r="L29" s="21"/>
     </row>
-    <row r="30" ht="18.75" spans="2:12">
+    <row r="30" customFormat="1" ht="14" customHeight="1" spans="2:12">
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="22"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31" ht="18.75" spans="2:12">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3239,7 +3353,7 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="F26:L30"/>
+    <mergeCell ref="F27:L31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
